--- a/artfynd/A 64023-2021 artfynd.xlsx
+++ b/artfynd/A 64023-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64023-2021 artfynd.xlsx
+++ b/artfynd/A 64023-2021 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 64023-2021 artfynd.xlsx
+++ b/artfynd/A 64023-2021 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
